--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PEDAL PARTIDA - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PEDAL PARTIDA - 01_02.xlsx
@@ -482,7 +482,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +507,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,7 +532,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +557,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +582,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -587,7 +607,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -608,7 +632,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -646,7 +674,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -663,7 +695,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PEDAL PARTIDA - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PEDAL PARTIDA - 01_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -653,11 +608,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -674,11 +624,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -693,11 +638,6 @@
       <c r="D12" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
     </row>
